--- a/data/docent/번역-작업지-지점원고.xlsx
+++ b/data/docent/번역-작업지-지점원고.xlsx
@@ -445,7 +445,7 @@
     <row r="1" ht="52" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 에 붙여 넣을 문장: "다음 성지 안내 원고를 {언어}로 번역해 줘. 안내자가 옆에서 말하는 존댓말 구어체('~보세요', '~입니다')를 살리고, 문장 수와 순서를 그대로 유지해. 고유명사(성인·신부 이름, 지명)는 가톨릭 {언어} 표기를 따라." — 결과를 그 언어 칸에 붙여 넣는다. 한 줄 = 한 지점. 이미 영어가 있는 줄은 en 칸이 채워져 있다.</t>
+          <t>AI 에 붙여 넣을 문장: "다음 성지 안내 원고를 {언어}로 번역해 줘. 안내자가 옆에서 말하는 존댓말 구어체('~보세요', '~입니다')를 살리고, 문장 수와 순서를 그대로 유지해. 고유명사(성인·신부 이름, 지명)는 가톨릭 {언어} 표기를 따라." — 결과를 그 언어 칸에 붙여 넣는다. 한 줄 = 한 지점. en(영어)은 전부 채워져 있으니 it·fr·pt·es 만 하면 된다.</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,11 @@
           <t>저와 함께 두 첨탑에서 유리화, 마당의 십자가까지 살펴보겠습니다. 건물과 빛 속에 남은 대구 신앙 공동체의 이야기를 만나 보세요.</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr"/>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Let me walk you from the twin spires to the stained glass and out to the cross in the courtyard — the story of Daegu's Catholic community, kept in building and light.</t>
+        </is>
+      </c>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr"/>
@@ -572,7 +576,11 @@
           <t>먼저 성당 정면의 두 첨탑을 올려다보세요. 한옥 성당이 불탄 뒤 공동체가 다시 지은 벽돌 성당입니다. 처음부터 지금 모습은 아니었고, 신자가 늘면서 종탑을 높이고 건물을 넓혔습니다. 저는 두 탑 사이의 둥근 장미창도 함께 보시길 권합니다. 위로 뻗는 첨탑과 꽃처럼 펼쳐진 창을 차례로 보면 건물의 다른 표정이 드러납니다.</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr"/>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Begin by looking up at the two spires on the façade. This brick church was rebuilt by the community after the earlier hanok church burned down. It did not start out this way: as the congregation grew, the bell towers were raised and the building widened. I also suggest you take in the round rose window between the towers. Look at the spires reaching upward, then at the window opening like a flower, and the building shows you two different faces.</t>
+        </is>
+      </c>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
@@ -606,7 +614,11 @@
           <t>제대 뒤의 긴 창들을 바라보세요. 이곳의 오래된 유리화는 프랑스 툴루즈의 제스타 공방에서 만들어 대구로 들여온 작품입니다. 저는 인물의 얼굴에서 시선을 조금 옮겨 창 위아래의 꽃과 잎 장식을 찾아보시길 권합니다. 빛을 받아 드러나는 색과 식물 무늬가 성인의 모습을 감싸고 있습니다. 먼 공방의 손길이 이곳 기도 공간에 남아 있는 셈입니다.</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr"/>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Look at the tall windows behind the altar. These old stained-glass panels were made in the Gesta workshop in Toulouse, France, and brought to Daegu. Let your eyes drift from the faces of the figures to the flowers and leaves at the top and bottom of each window. As the light comes through, the colors and plant patterns wrap around the saints. The hand of a faraway workshop still rests in this place of prayer.</t>
+        </is>
+      </c>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
@@ -640,7 +652,11 @@
           <t>성당 앞마당의 큰 십자가를 찾아보세요. 초대 교구장 드망즈 주교의 부임 스물다섯 해를 기념해 세운 십자가입니다. 그 시간은 대구 교구가 생기고 계산성당이 주교좌성당이 된 역사와도 이어집니다. 저는 십자가를 본 뒤 그 너머의 성당까지 함께 바라보시길 권합니다. 마당의 기념물 하나가 이곳이 지역 교회의 중심으로 자란 시간을 들려줍니다.</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr"/>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Find the large cross in the front yard. It was raised to mark twenty-five years since Bishop Demange, the first bishop of Daegu, took office. Those years run alongside the birth of the Diocese of Daegu and Gyesan becoming its cathedral. After you look at the cross, let your gaze carry on to the church behind it. One monument in the yard tells how this place grew into the heart of the local Church.</t>
+        </is>
+      </c>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
@@ -674,7 +690,11 @@
           <t>두 탑과 유리창, 마당의 십자가를 지나왔습니다. 골목으로 돌아서기 전에 서로 다른 손길이 남은 성당을 한 번 더 바라보세요.</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>We have passed the two towers, the windows and the cross in the yard. Before you turn back into the lane, look once more at a church shaped by so many different hands.</t>
+        </is>
+      </c>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
@@ -710,7 +730,7 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>Welcome to Gongseri in Asan. On this hill, ringed by trees more than three centuries old, stands a red-brick Gothic church. In the Joseon era this was the site of a granary that gathered tax rice from forty counties of Chungcheong, and because sea and land met here, missionaries and messengers slipped through this port. Today we will walk past the church, the martyrs' graves, and one unexpected story born in this village.</t>
+          <t>Welcome to Gongseri Shrine Church. Together we will look at the church built on the site of an old grain warehouse, the space honoring the martyrs, and the village story that continues in the old rectory.</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr"/>
@@ -748,7 +768,7 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>Before climbing to the church, look up at these trees. Hackberries and zelkovas have guarded this hill for more than three hundred years. The name Gongseri comes from the 'Gongse-chang', the granary where tax rice owed to the state was collected. Built in the reign of King Seongjong, it gathered rice from thirty-nine counties of Chungcheong and shipped it by boat to the Han River. After the granary closed, the parish bought the site in 1895 and moved here. A hill where taxes were gathered became a hill where prayers gather.</t>
+          <t>On the path up to the church, take in the great trees and the shape of the hill together. This area was the site of Gongse-chang, the state granary where grain owed in tax was gathered. Close to Asan Bay, tax rice from many counties was collected here; after the warehouse was gone, the church and rectory took its place. Remember the trace of the warehouse kept in the name Gongseri, and the church among the trees looks different, part of the village's long history.</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr"/>
@@ -786,7 +806,7 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>The church before you was designed by Father Émile Devise of the Paris Foreign Missions and completed in 1922. A pointed bell tower rises over red brick, and the windows end in pointed arches. Imagine the faces of villagers a century ago when such a building rose on a rural hill. It is Chungcheongnam-do Monument No. 144, and the Korea Tourism Organization once named it among the most beautiful churches representing Korea. Films and dramas have borrowed this forecourt many times.</t>
+          <t>From the front, look up at the bell tower and then at the windows. The present church was designed by Father Devise and completed in 1922. Chinese craftsmen took part in the construction, and at the time it was striking enough that people came just to look at it. Study the building slowly, comparing how small units of red brick add up to a great wall, and how its lines narrow as they rise.</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr"/>
@@ -824,7 +844,7 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>Thirty-two martyrs rest in this burial ground beside the church — people seized in the Naepo region and killed for their faith between the Sinyu Persecution of 1801 and 1873. Among them are three brothers, Bak Ui-seo, Bak Won-seo and Bak Ik-seo, martyred together in the Byeongin Persecution of 1867. Pause a moment and consider what it means for brothers to die on the same day for what they believed. The memorial tower carries their names so they are not forgotten.</t>
+          <t>In front of the memorial tower, turn your eyes from the building to the names left here. This is the place that remembers the martyrs of the Gongseri area in Asan. The three Bak brothers from Geolmae-ri were arrested together, taken to Suwon and died there for keeping their faith. Rather than thinking of martyrdom as an event from a distant age, try to picture it as the story of a family that lived in this very village.</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr"/>
@@ -862,7 +882,7 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>This small building behind the church is a museum made from the old rectory where the priests once lived. Inside are the remains of the three Bak brothers and the everyday belongings of the hidden Catholic villages of the persecution era. Worn bowls and clothes linger in the memory longer than any gilded object. You are looking at objects from a hundred and fifty years ago inside a building more than a century old — take your time.</t>
+          <t>Look at the museum building from the outside first. It was originally the rectory where the priests lived, later converted into an exhibition space. Standing beside the church, the building now passes on the history of the martyrs and of the parish. If you can see the exhibits, look for the materials on how the church was built. The brick building you saw in the yard a moment ago, made by someone's design and labor, comes suddenly close.</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr"/>
@@ -900,7 +920,7 @@
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>One last, unexpected story. Father Devise, who designed the church, was also skilled in medicine and treated villagers' boils and wounds with an ointment. The parishioner who learned his recipe was John Yi Myeong-rae, and what he made became the 'Yi Myeong-rae Ointment' found in every Korean pharmacy a generation ago. That black plaster people pressed onto wounds began, in a sense, in this churchyard. It is a story of how faith touched a village where it hurt — worth a smile even if you are not a believer.</t>
+          <t>If the exhibits include the story of the Yi Myeong-rae ointment, pause over it. Father Devise made an ointment for villagers suffering from boils, and Yi Myeong-rae, who worked at the church, is said to have learned how to make it. Behind a familiar medicine's name hides a bond between the church and the village. Alongside the history of the great building, the everyday care of neighbors' ailments also remains in this place.</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr"/>
@@ -938,7 +958,7 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>Thank you for walking Gongseri with us. Within a thirty-minute drive are Solmoe, birthplace of St. Andrew Kim Taegon, and Sinri, the shrine of Bishop Daveluy. Link the three and you have a single day's walk through the roots of faith in Naepo. Peace on your journey.</t>
+          <t>Thank you for walking Gongseri with me. As you leave the old trees, the church and the place that remembers the martyrs, hold on to the scene that stayed with you today.</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr"/>
@@ -1240,7 +1260,11 @@
           <t>저와 함께 정면의 종탑, 성당 안의 유리화, 광장의 조형물을 살펴보겠습니다. 항구 도시 한가운데 이어져 온 신앙의 흔적을 찾아보세요.</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr"/>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>Let me walk you from the bell towers on the façade to the stained glass inside and the sculptures on the square — traces of a faith that has lived on in the middle of a port city.</t>
+        </is>
+      </c>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
@@ -1274,7 +1298,11 @@
           <t>성당 정면에서 가운데 큰 종탑과 양옆의 작은 종탑을 차례로 바라보세요. 붉은 벽돌 건물에 세 탑이 균형을 이루는 모습이 답동성당의 특징입니다. 옛 성당을 두고 바깥쪽을 넓힌 공사를 거쳐 지금 모습이 됐습니다. 저는 창의 둥근 윗부분과 밝은 화강석 테두리도 찾아보시길 권합니다. 벽돌과 돌이 만나는 자리에서 건축의 표정이 또렷해집니다.</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr"/>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>From the front, look at the large central bell tower, then the smaller ones on either side. Three towers in balance on a red-brick body — that is the signature of Dapdong. The church reached its present form when the outer walls were extended around the older building. I also suggest you find the rounded tops of the windows and the pale granite edging around them. Where brick meets stone, the building's expression comes into focus.</t>
+        </is>
+      </c>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
@@ -1308,7 +1336,11 @@
           <t>성당 안에서는 제대 뒤로 들어오는 색빛을 바라보세요. 이 유리화는 본당 설립 아흔 해를 기념하며 만든 작품입니다. 처음에는 추상적인 색과 선처럼 보이지만, 제대 뒤 창에는 장미 무늬가 담겨 있습니다. 저는 선을 천천히 따라가며 꽃의 형태를 찾아보시길 권합니다. 양옆 창에는 예수의 수난과 부활 이야기도 담겨 있어 빛을 통해 성경을 전합니다.</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr"/>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>Inside, look at the colored light falling through the window behind the altar. This glass was made to mark ninety years since the parish was founded. At first it looks like abstract color and line, but a rose is set into the window behind the altar. Follow the lines slowly and let the flower take shape. The side windows carry the Passion and Resurrection of Jesus, so the Scriptures arrive here through light.</t>
+        </is>
+      </c>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
@@ -1342,7 +1374,11 @@
           <t>광장에서는 십자가의 길을 표현한 청동 조형물을 찾아보세요. 예수가 고난을 겪으며 걸어간 여정을 새긴 작품들입니다. 성당 일대를 시민들이 쉬고 역사를 만나는 공간으로 정비하면서 이 길도 마련했습니다. 저는 한 장면 앞에 잠시 멈춰 인물들의 몸짓을 살펴보시길 권합니다. 시장과 거리로 이어지는 광장에서 고통과 돌봄의 이야기를 만날 수 있습니다.</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr"/>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>On the square, find the bronze sculptures of the Way of the Cross. They depict the journey Jesus walked through his suffering. The path was laid out when the area around the church was remade as a place for citizens to rest and meet its history. Stop in front of one scene and study the gestures of the figures. On a square that opens onto the market and the street, you meet a story of pain and of care.</t>
+        </is>
+      </c>
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
@@ -1376,7 +1412,11 @@
           <t>성당의 탑과 유리화, 광장의 이야기를 함께 보았습니다. 돌아가는 길에는 거리와 성당이 만나는 풍경도 눈여겨보세요.</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr"/>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>We have seen the towers, the glass and the story of the square. On your way back, notice too where the street and the church meet.</t>
+        </is>
+      </c>
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
@@ -1412,7 +1452,7 @@
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>Welcome to Daeheung-dong Church in Daejeon — the city's first parish, founded in 1919, and today the cathedral of the Diocese of Daejeon. When this building was completed in 1962 it was the tallest structure in downtown Daejeon. For sixty years, as the city grew up around it, the bell tower has stood in the same place. Today we walk from outside to inside, from the tower to the altar.</t>
+          <t>Welcome to Daeheung-dong Church. As we look at the bell tower, the sculptures and the space inside, let us hear how this church became part of everyday life in Daejeon.</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr"/>
@@ -1450,7 +1490,7 @@
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>Before going in, look at the façade from across the street. The roof rises from both sides toward the center and points to the sky — people say the building was shaped after two hands joined in prayer. The architect was Lee Chang-geun (Don Bosco), and the drawings were even sent to Rome. Ground was broken in 1960, halted by a dispute among builders, then finished in nine months on 30 December 1962. It was the tallest building in Daejeon then; onlookers who came to watch the tower rise said it made them dizzy. Today it is Registered Cultural Heritage No. 643.</t>
+          <t>From the front, look up at the bell tower. Beyond its height, try to imagine the sound that once rang out from it. For the people of Daeheung-dong the bell announced mealtimes and gave a brief pause to a busy day. For many years someone pulled the rope by hand; today the bell rings automatically. To the eye that studies the building, add an ear for the daily life of the city.</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr"/>
@@ -1488,7 +1528,7 @@
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>Standing at the main door, the canopy blocks the view and most people simply walk in. Step back and look up. Above the entrance, relief figures of the twelve apostles stand in a row. They were made jointly by Lee Nam-kyu, later famous for stained glass, and the sculptor Choi Jong-tae — both still young and unknown at the time; hiring young artists for a cathedral was itself daring in those days. It is the easiest thing here to miss, and the thing you look at longest once you know.</t>
+          <t>Look slowly at the wall above the entrance canopy. Carved in relief, standing out from the wall, are the twelve apostles. Lee Nam-kyu and Choi Jong-tae made them together when both were still young. It is a sculpture easy to miss if you walk in with your eyes down, yet it carries the most important story on the church's face. Compare the faces and gestures one by one and find how different each figure is within the same row.</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr"/>
@@ -1526,7 +1566,7 @@
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>Come inside and let your eyes adjust. Then look all the way up: this wide hall has not a single pillar — a feat for the early 1960s that architectural historians still note. Along both walls the fourteen Stations of the Cross are carved in large relief, and in the 1970s Father André Bouton, a French Benedictine, painted vivid murals on those walls. What remains today is part of that work; restoration is under way. Until 1985 the wall behind the altar was stained glass; it has since changed.</t>
+          <t>Inside, first take in the view that runs from the ceiling all the way to the altar. What sets this building apart is that not a single pillar interrupts the wide space. Outside, the height of the tower draws the eye; inside, it is the openness you feel first. Toward the altar, murals by Father André Bouton remain on the wall. Once you have taken in the structure of the great space, let your gaze move to the bold lines and colors of the painting.</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr"/>
@@ -1564,7 +1604,7 @@
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>Beneath the pine in the courtyard sits a statue of a mother holding her son. Lee Nam-kyu made it in 1964 to mark 180 years of Catholicism in Korea. Her face and robes are those of a Korean woman rather than a Western Madonna, which surprises some first-time visitors — yet the parishioners have grown so attached to her that they refuse to have her moved. To anyone who has lost a child, or a mother, this place speaks regardless of religion.</t>
+          <t>Stand facing the statue of Mary in the courtyard and study the lines of her face. Made by Lee Nam-kyu, this figure may look unfamiliar to anyone used to smooth, gentle Madonnas. Some read in her plain, sturdy expression the lives of Korean mothers who cared for their families after the war. Rather than settling on an answer first, look slowly at the balance of face and body and feel what this figure conveys to you.</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr"/>
@@ -1602,7 +1642,7 @@
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>A few minutes' walk from the church is Daejeon's most famous bakery, Sungsimdang. Its name, 'Sungsim', comes from the Sacred Heart of Jesus. The story goes that in 1956 the founder, a war refugee, received two sacks of flour from the priest of this very church and began selling steamed buns in front of the station. To this day the bakery gives its unsold bread to neighbors. A bread story that began at a church — you might end your pilgrimage there.</t>
+          <t>Look out toward the lane and think of how the nearby bakery Sungsimdang began. After the war, two sacks of flour shared by this church were turned into steamed buns — that was its start. The founder gave unsold bread to neighbors, and the bakery's habit of sharing has lasted for decades. The bell tower is not the only thing that became part of the city's landscape. A hand passing out a little food also became a story that ties the church to its neighborhood.</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr"/>
@@ -1640,7 +1680,7 @@
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>Thank you for walking Daeheung-dong with us. Within an hour of Daejeon begins the Naepo pilgrimage route — Solmoe, Gongseri and Haemi. From a city cathedral to shrines in the fields: may your journey continue.</t>
+          <t>Thank you for spending this time at Daeheung-dong. Carry the sound of its bell, its works of art and the story of sharing that reached the neighborhood with you on the road ahead.</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr"/>
@@ -4602,7 +4642,11 @@
           <t>저와 함께 한옥 성당에서 서양식 성당으로 시선을 옮겨 보겠습니다. 서로 다른 건물에 남은 한 공동체의 이야기를 만나 보세요.</t>
         </is>
       </c>
-      <c r="G111" s="1" t="inlineStr"/>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>Let me move your eyes from the hanok church to the Western-style church beside it — one community's story, kept in two very different buildings.</t>
+        </is>
+      </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr"/>
       <c r="J111" s="1" t="inlineStr"/>
@@ -4636,7 +4680,11 @@
           <t>마당에서 한옥의 기와지붕과 서양식 성당을 함께 바라보세요. 문산성당은 살림집을 고쳐 기도하던 시절을 지나, 신자들이 늘면서 새로운 성당을 지었습니다. 옛 한옥 건물은 남아 공동체의 시간을 이어 줍니다. 저는 지붕의 선을 서로 비교해 보시길 권합니다. 익숙한 한옥과 서양에서 들어온 건축 방식이 같은 마당에 있어 신앙이 자리를 잡아 간 과정을 보여 줍니다.</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr"/>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>From the yard, take in the tiled roof of the hanok and the Western-style church together. Munsan began with prayers in a converted house; as the faithful grew, they built a new church. The old hanok building remains, carrying the community's years forward. Compare the lines of the two roofs. A familiar Korean roof and an architecture brought from the West share one yard, and together they show how the faith settled here.</t>
+        </is>
+      </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr"/>
       <c r="J112" s="1" t="inlineStr"/>
@@ -4670,7 +4718,11 @@
           <t>서양식 성당의 벽과 입구를 바라보세요. 새 성당을 지을 때 김영제 신부는 재산과 오토바이를 팔아 비용을 보탰고, 신자들은 시멘트와 벽돌을 직접 날랐습니다. 그렇게 힘을 모아 1937년 성당을 봉헌했습니다. 저는 건물의 크기보다 벽을 이루는 작은 단위들에 눈길을 두고 싶습니다. 사람들이 손수 나른 재료가 모여 함께 기도할 집이 된 이야기입니다.</t>
         </is>
       </c>
-      <c r="G113" s="1" t="inlineStr"/>
+      <c r="G113" s="1" t="inlineStr">
+        <is>
+          <t>Look at the wall and the entrance of the Western-style church. When the new church was built, Father Kim Yeong-je sold his property and even his motorcycle to help pay for it, and parishioners carried the cement and bricks themselves. Gathering their strength that way, they consecrated the church in 1937. Rather than the size of the building, I would rest your eyes on the small units that make up the wall. Materials carried by hand became a house where people could pray together.</t>
+        </is>
+      </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr"/>
       <c r="J113" s="1" t="inlineStr"/>
@@ -4704,7 +4756,11 @@
           <t>성당 안에서 기둥이 이어지는 방향을 따라 제대 쪽을 바라보세요. 가운데와 양옆으로 공간이 나뉘는 구조를 볼 수 있습니다. 제대 뒤 벽에는 부활한 그리스도와 열두 사도를 그린 성화가 있습니다. 본당 백주년을 전후해 내부를 가꾸며 마련한 모습입니다. 저는 먼저 전체 구도를 본 다음 인물들의 표정을 살펴보시길 권합니다. 오래된 건물 안에 후대의 손길이 겹쳐 있습니다.</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr"/>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>Inside, follow the line of pillars toward the altar. You can see how the space divides into a center and two sides. On the wall behind the altar is a painting of the risen Christ with the twelve apostles, added when the interior was renewed around the parish's centenary. Take in the whole composition first, then look at the expressions of the figures. Inside an old building, a later generation's hands are laid over the earlier ones.</t>
+        </is>
+      </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr"/>
       <c r="J114" s="1" t="inlineStr"/>
@@ -4738,7 +4794,11 @@
           <t>두 성당을 둘러보았습니다. 마당으로 나오면 다른 지붕 아래 같은 공동체의 시간이 이어져 있다는 이야기를 떠올려 보세요.</t>
         </is>
       </c>
-      <c r="G115" s="1" t="inlineStr"/>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>We have looked at both churches. As you step back into the yard, remember that under two different roofs runs the time of one and the same community.</t>
+        </is>
+      </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr"/>
       <c r="J115" s="1" t="inlineStr"/>
@@ -4772,7 +4832,11 @@
           <t>풍수원에서는 산골 교우촌이 남긴 성당과 생활의 흔적을 만나겠습니다. 벽돌 외벽과 나무 천장, 옛 사제관을 차례로 살펴보며 이 공간을 함께 지킨 사람들을 떠올려 보세요.</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr"/>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>At Pungsuwon we meet the church and the traces of daily life left by a mountain village of believers. Look in turn at the brick walls, the wooden ceiling and the old rectory, and think of the people who kept this place together.</t>
+        </is>
+      </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr"/>
       <c r="J116" s="1" t="inlineStr"/>
@@ -4806,7 +4870,11 @@
           <t>성당의 붉은 벽돌과 회색 벽돌을 눈여겨보세요. 정규하 신부가 건립을 이끌었고, 신자들도 건축재료를 마련하며 공사에 참여했습니다. 피난해 온 사람들이 모여 살던 마을에서, 함께 예배할 집을 세운 것입니다. 종탑만 올려다보기보다 벽돌이 이어지는 벽면과 둥근 창을 차례로 살펴보세요. 이 성당은 서양의 건축 모습을 받아들이면서도, 그 재료와 노동을 마련한 지역 사람들의 손길을 담고 있습니다.</t>
         </is>
       </c>
-      <c r="G117" s="1" t="inlineStr"/>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>Notice the red and grey bricks of the church. Father Jeong Gyu-ha led the construction, and the parishioners took part too, gathering building materials themselves. In a village settled by people who had fled persecution, they raised a house to worship in together. Rather than only looking up at the bell tower, follow the brick wall and the rounded windows in turn. This church took on a Western form, yet it holds the hands of local people who supplied its materials and its labor.</t>
+        </is>
+      </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr"/>
       <c r="J117" s="1" t="inlineStr"/>
@@ -4840,7 +4908,11 @@
           <t>안으로 들어가면 나란히 선 기둥 위의 둥근 천장을 바라보세요. 서양 성당의 모습을 닮았지만, 이 천장은 무거운 돌이 아니라 나무로 만들었습니다. 전통 대들보 공법을 응용하고, 둥글게 휜 널판을 연결해 모양을 냈습니다. 당시의 경제적 여건과 건축 기술 안에서 찾은 방법입니다. 제단까지 이어지는 기둥의 줄과 천장의 곡선을 함께 보면, 익숙한 목재가 새로운 공간을 만든 모습을 만날 수 있습니다.</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr"/>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>Step inside and look at the rounded ceiling above the rows of pillars. It resembles a Western church, but this vault is made of wood, not heavy stone. Builders adapted the traditional Korean beam method and joined curved planks to shape it — a solution found within the means and the skills of the time. Take in the line of pillars running to the altar together with the curve of the ceiling, and you see a familiar material making a new kind of space.</t>
+        </is>
+      </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr"/>
       <c r="J118" s="1" t="inlineStr"/>
@@ -4874,7 +4946,11 @@
           <t>성당 곁의 옛 사제관을 바라보세요. 사제관은 신부가 일하고 생활하던 집입니다. 예배를 드리는 성당 옆에 이런 집이 있다는 사실은, 신앙이 마을 사람들을 만나고 일상을 돌보는 일과 함께 이어졌음을 생각하게 합니다. 이 건물은 복원을 거쳐 2018년 풍수원성당 역사관으로 문을 열었습니다. 벽돌로 된 집의 외관을 살피며, 성당과 생활 공간이 나란히 지켜 온 공동체의 시간을 떠올려 보세요.</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr"/>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>Look at the old rectory beside the church. A rectory is the house where the priest worked and lived. That such a house stands next to the place of worship reminds us that faith here went hand in hand with meeting the villagers and caring for everyday life. After restoration, the building opened in 2018 as the Pungsuwon Church history hall. As you study the brick house, think of the community whose years the church and the home kept side by side.</t>
+        </is>
+      </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr"/>
       <c r="J119" s="1" t="inlineStr"/>
@@ -4908,7 +4984,11 @@
           <t>붉은 벽돌과 나무 천장, 신부가 살던 집까지 돌아보았습니다. 풍수원은 건물의 아름다움과 그 안에서 이어진 공동체의 삶을 함께 기억하게 하는 곳입니다.</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>We have walked past the red brick, the wooden ceiling and the house where the priest lived. Pungsuwon lets you remember the beauty of the building and the life of the community that went on inside it, both at once.</t>
+        </is>
+      </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr"/>
       <c r="J120" s="1" t="inlineStr"/>
@@ -5183,7 +5263,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
